--- a/other/001_youth_climate_policy_understanding_survey--student_assessment_forms.xlsx
+++ b/other/001_youth_climate_policy_understanding_survey--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_questions</t>
+          <t>climate_policy_awareness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey Questions</t>
+          <t>Climate policy awareness</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>climate_knowledge</t>
+          <t>climate_policy_attitudes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Climate Knowledge</t>
+          <t>Attitudes towards climate policy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>climate_actions</t>
+          <t>climate_policy_participation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Climate Actions</t>
+          <t>Climate policy participation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>climate_impacts</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Climate Impacts</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>policy_awareness</t>
+          <t>climate_policy_knowledge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Policy Awareness</t>
+          <t>Climate policy knowledge</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>policy_support</t>
+          <t>climate_policy_solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Policy Support</t>
+          <t>Climate policy solutions</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>policy_participation</t>
+          <t>climate_policy_government_role</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Policy Participation</t>
+          <t>Government role in climate policy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>climate_emotions</t>
+          <t>climate_policy_participation_history</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Climate Emotions</t>
+          <t>Climate policy participation history</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>policy_opinions</t>
+          <t>climate_policy_application</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Policy Opinions</t>
+          <t>Climate policy application</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,131 +727,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>policy_recommendations</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Policy Recommendations</t>
+          <t>Confidence in applying climate policy principles</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>other_comments</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Other Comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>climate_knowledge_important</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Climate Knowledge Important</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>survey_comments</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Survey Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>demographic_info</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Demographic Information</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Contact Information</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,204 +781,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>climate_knowledge_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>ngos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NGOs</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>climate_knowledge_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>schools</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>climate_actions_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>advocacy_groups</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>climate_actions_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>policy_support_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>policy_support_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>policy_participation_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>policy_participation_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>climate_emotions_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>climate_emotions_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>climate_knowledge_important_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>climate_knowledge_important_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>not_important</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Not Important</t>
+          <t>advocacy groups</t>
         </is>
       </c>
     </row>
